--- a/docs/lem/files/xslope_low_clay.xlsx
+++ b/docs/lem/files/xslope_low_clay.xlsx
@@ -5721,7 +5721,9 @@
       <c r="K11" s="3">
         <v>0.0</v>
       </c>
-      <c r="L11" s="3" t="n"/>
+      <c r="L11" s="3">
+        <v>0.0</v>
+      </c>
       <c r="M11" s="3">
         <v>125000.0</v>
       </c>
@@ -5845,7 +5847,9 @@
       <c r="K12" s="3">
         <v>0.0</v>
       </c>
-      <c r="L12" s="3" t="n"/>
+      <c r="L12" s="3">
+        <v>0.0</v>
+      </c>
       <c r="M12" s="3">
         <v>8000.0</v>
       </c>
@@ -5969,7 +5973,9 @@
       <c r="K13" s="3">
         <v>0.0</v>
       </c>
-      <c r="L13" s="3" t="n"/>
+      <c r="L13" s="3">
+        <v>0.0</v>
+      </c>
       <c r="M13" s="3">
         <v>8000.0</v>
       </c>
